--- a/data/Second_Paper_MILP_Dataset_Full.xlsx
+++ b/data/Second_Paper_MILP_Dataset_Full.xlsx
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="P2" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q2" s="1" t="n">
         <v>5</v>
@@ -1423,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="P3" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="1" t="n">
         <v>4</v>
@@ -1479,7 +1479,7 @@
         <v>1</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" s="1" t="n">
         <v>4</v>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" s="1" t="n">
         <v>4</v>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="P6" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>3</v>
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="1" t="n">
         <v>3</v>
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q8" s="1" t="n">
         <v>3</v>
@@ -1759,7 +1759,7 @@
         <v>1</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>3</v>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="1" t="n">
         <v>4</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="P11" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" s="1" t="n">
         <v>5</v>
@@ -1927,7 +1927,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q12" s="1" t="n">
         <v>4</v>
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="P13" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q13" s="1" t="n">
         <v>4</v>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="P14" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q14" s="1" t="n">
         <v>4</v>
@@ -2095,7 +2095,7 @@
         <v>0</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q15" s="1" t="n">
         <v>5</v>
@@ -2151,7 +2151,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="1" t="n">
         <v>4</v>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="P17" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q17" s="1" t="n">
         <v>4</v>
@@ -2263,7 +2263,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="1" t="n">
         <v>3</v>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
       <c r="P19" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q19" s="1" t="n">
         <v>4</v>
@@ -2375,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="P20" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q20" s="1" t="n">
         <v>4</v>
@@ -2431,7 +2431,7 @@
         <v>1</v>
       </c>
       <c r="P21" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q21" s="1" t="n">
         <v>4</v>
@@ -2487,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="P22" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="1" t="n">
         <v>4</v>
@@ -2543,7 +2543,7 @@
         <v>1</v>
       </c>
       <c r="P23" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q23" s="1" t="n">
         <v>4</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="P24" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="1" t="n">
         <v>4</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="P25" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="1" t="n">
         <v>4</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="P26" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q26" s="1" t="n">
         <v>4</v>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="P27" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q27" s="1" t="n">
         <v>5</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="P28" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="1" t="n">
         <v>5</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="P29" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="1" t="n">
         <v>5</v>
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q30" s="1" t="n">
         <v>5</v>
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
       <c r="P31" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q31" s="1" t="n">
         <v>5</v>
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" s="1" t="n">
         <v>5</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="P33" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q33" s="1" t="n">
         <v>4</v>
@@ -3159,7 +3159,7 @@
         <v>0</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q34" s="1" t="n">
         <v>5</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q35" s="1" t="n">
         <v>5</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="P36" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q36" s="1" t="n">
         <v>5</v>
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="P37" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="1" t="n">
         <v>4</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" s="1" t="n">
         <v>5</v>
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q39" s="1" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="1" t="n">
         <v>4</v>
@@ -3557,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="P41" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" s="1" t="n">
         <v>4</v>
@@ -3616,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="P42" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q42" s="1" t="n">
         <v>4</v>
@@ -3675,7 +3675,7 @@
         <v>1</v>
       </c>
       <c r="P43" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q43" s="1" t="n">
         <v>4</v>
@@ -3734,7 +3734,7 @@
         <v>1</v>
       </c>
       <c r="P44" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q44" s="1" t="n">
         <v>4</v>
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q45" s="1" t="n">
         <v>4</v>
@@ -3852,7 +3852,7 @@
         <v>1</v>
       </c>
       <c r="P46" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q46" s="1" t="n">
         <v>3</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="1" t="n">
         <v>3</v>
@@ -3967,7 +3967,7 @@
         <v>1</v>
       </c>
       <c r="P48" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="1" t="n">
         <v>4</v>
@@ -4023,7 +4023,7 @@
         <v>1</v>
       </c>
       <c r="P49" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="1" t="n">
         <v>5</v>
@@ -4079,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="P50" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q50" s="1" t="n">
         <v>4</v>
@@ -4135,7 +4135,7 @@
         <v>1</v>
       </c>
       <c r="P51" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q51" s="1" t="n">
         <v>4</v>
